--- a/invoice_agent/exgrowth_202610.xlsx
+++ b/invoice_agent/exgrowth_202610.xlsx
@@ -498,6 +498,11 @@
       <c r="H2" s="1" t="n">
         <v>46326</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>メール配信サポート対象：インダストリア様、BNE様、DFT様、日本電力調達ソリューション様</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>メール配信サポート</t>
+          <t>4社分、メール配信サポート（対象は備考参照）</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/invoice_agent/exgrowth_202610.xlsx
+++ b/invoice_agent/exgrowth_202610.xlsx
@@ -498,11 +498,6 @@
       <c r="H2" s="1" t="n">
         <v>46326</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>メール配信サポート対象：インダストリア様、BNE様、DFT様、日本電力調達ソリューション様</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,7 +510,8 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4社分、メール配信サポート（対象は備考参照）</t>
+          <t>インダストリア・BNE・DFT・
+日本電力調達ソリューション分、メール配信サポート</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/invoice_agent/exgrowth_202610.xlsx
+++ b/invoice_agent/exgrowth_202610.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
     </row>
   </sheetData>
